--- a/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
+++ b/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
@@ -214,7 +214,7 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Rained Out</t>
         </is>
       </c>
     </row>
@@ -355,21 +355,21 @@
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October 31, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>14:00 EDT</t>
+          <t>08:45 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,27 +394,27 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
         <is>
-          <t>08:45 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D8" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="E8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>River Island FC 2015/2016 RAVENS</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -439,17 +439,17 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November 15, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>River Island FC 2015/2016 RAVENS</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
+          <t>Red Hook Ball Fields 7 - 11v11, 9v9, 7v7 (1)</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
+++ b/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
@@ -175,26 +175,26 @@
     </row>
     <row r="3">
       <c r="A3" s="0" t="n">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B3" s="0" t="inlineStr">
         <is>
-          <t>Saturday, September 26, 2026</t>
+          <t>Saturday, October  3, 2026</t>
         </is>
       </c>
       <c r="C3" s="0" t="inlineStr">
         <is>
-          <t>13:30 EDT</t>
+          <t>08:30 EDT</t>
         </is>
       </c>
       <c r="D3" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>River Island FC 2015/2016 RAVENS</t>
         </is>
       </c>
       <c r="E3" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>1 - 0</t>
         </is>
       </c>
       <c r="F3" s="0" t="inlineStr">
@@ -204,7 +204,7 @@
       </c>
       <c r="G3" s="0" t="inlineStr">
         <is>
-          <t>Dyker Turf Field B Small Sided  - B</t>
+          <t>Jack McManus Field - Jack McManus/Octagon Field</t>
         </is>
       </c>
       <c r="H3" s="0" t="inlineStr">
@@ -214,42 +214,42 @@
       </c>
       <c r="I3" s="0" t="inlineStr">
         <is>
-          <t>Rained Out</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="n">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="B4" s="0" t="inlineStr">
         <is>
-          <t>Saturday, October  3, 2026</t>
+          <t>Sunday, October  4, 2026</t>
         </is>
       </c>
       <c r="C4" s="0" t="inlineStr">
         <is>
-          <t>08:30 EDT</t>
+          <t>08:00 EDT</t>
         </is>
       </c>
       <c r="D4" s="0" t="inlineStr">
         <is>
-          <t>River Island FC 2015/2016 RAVENS</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="E4" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 - 6</t>
         </is>
       </c>
       <c r="F4" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="G4" s="0" t="inlineStr">
         <is>
-          <t>Jack McManus Field - Jack McManus/Octagon Field</t>
+          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
         </is>
       </c>
       <c r="H4" s="0" t="inlineStr">
@@ -259,22 +259,22 @@
       </c>
       <c r="I4" s="0" t="inlineStr">
         <is>
-          <t>Rescheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="n">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="B5" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October  4, 2026</t>
+          <t>Sunday, October 25, 2026</t>
         </is>
       </c>
       <c r="C5" s="0" t="inlineStr">
         <is>
-          <t>08:00 EDT</t>
+          <t>14:00 EDT</t>
         </is>
       </c>
       <c r="D5" s="0" t="inlineStr">
@@ -289,7 +289,7 @@
       </c>
       <c r="F5" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>FC Copa Academy Brooklyn B14/15 Black</t>
         </is>
       </c>
       <c r="G5" s="0" t="inlineStr">
@@ -310,21 +310,21 @@
     </row>
     <row r="6">
       <c r="A6" s="0" t="n">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="B6" s="0" t="inlineStr">
         <is>
-          <t>Sunday, October 25, 2026</t>
+          <t>Sunday, November  8, 2026</t>
         </is>
       </c>
       <c r="C6" s="0" t="inlineStr">
         <is>
-          <t>14:00 EDT</t>
+          <t>08:45 EST</t>
         </is>
       </c>
       <c r="D6" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>UNITED CYCLONES FC Geo 2014/15</t>
         </is>
       </c>
       <c r="E6" s="0" t="inlineStr">
@@ -334,12 +334,12 @@
       </c>
       <c r="F6" s="0" t="inlineStr">
         <is>
-          <t>FC Copa Academy Brooklyn B14/15 Black</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="G6" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
+          <t>Bill Brown Playground - 1</t>
         </is>
       </c>
       <c r="H6" s="0" t="inlineStr">
@@ -349,27 +349,27 @@
       </c>
       <c r="I6" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B7" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November  8, 2026</t>
+          <t>Sunday, November 15, 2026</t>
         </is>
       </c>
       <c r="C7" s="0" t="inlineStr">
         <is>
-          <t>08:45 EST</t>
+          <t>14:00 EST</t>
         </is>
       </c>
       <c r="D7" s="0" t="inlineStr">
         <is>
-          <t>UNITED CYCLONES FC Geo 2014/15</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="E7" s="0" t="inlineStr">
@@ -379,12 +379,12 @@
       </c>
       <c r="F7" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>River Island FC 2015/2016 RAVENS</t>
         </is>
       </c>
       <c r="G7" s="0" t="inlineStr">
         <is>
-          <t>Bill Brown Playground - 1</t>
+          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
         </is>
       </c>
       <c r="H7" s="0" t="inlineStr">
@@ -394,17 +394,17 @@
       </c>
       <c r="I7" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t/>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="n">
-        <v>444</v>
+        <v>438</v>
       </c>
       <c r="B8" s="0" t="inlineStr">
         <is>
-          <t>Sunday, November 15, 2026</t>
+          <t>Saturday, November 21, 2026</t>
         </is>
       </c>
       <c r="C8" s="0" t="inlineStr">
@@ -424,12 +424,12 @@
       </c>
       <c r="F8" s="0" t="inlineStr">
         <is>
-          <t>River Island FC 2015/2016 RAVENS</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="G8" s="0" t="inlineStr">
         <is>
-          <t>Prospect Park, Parade Grounds Field 10A - Parade Grounds Field 10A</t>
+          <t>Red Hook Ball Fields 7 - 11v11, 9v9, 7v7 (1)</t>
         </is>
       </c>
       <c r="H8" s="0" t="inlineStr">
@@ -439,27 +439,27 @@
       </c>
       <c r="I8" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="n">
-        <v>438</v>
+        <v>426</v>
       </c>
       <c r="B9" s="0" t="inlineStr">
         <is>
-          <t>Saturday, November 21, 2026</t>
+          <t>Sunday, December 13, 2026</t>
         </is>
       </c>
       <c r="C9" s="0" t="inlineStr">
         <is>
-          <t>14:00 EST</t>
+          <t>08:30 EST</t>
         </is>
       </c>
       <c r="D9" s="0" t="inlineStr">
         <is>
-          <t>Rebels Legacy Soccer Club 2014\2015</t>
+          <t>SC Gjoa Nyland</t>
         </is>
       </c>
       <c r="E9" s="0" t="inlineStr">
@@ -469,12 +469,12 @@
       </c>
       <c r="F9" s="0" t="inlineStr">
         <is>
-          <t>SC Gjoa Nyland</t>
+          <t>Rebels Legacy Soccer Club 2014\2015</t>
         </is>
       </c>
       <c r="G9" s="0" t="inlineStr">
         <is>
-          <t>Red Hook Ball Fields 7 - 11v11, 9v9, 7v7 (1)</t>
+          <t>Dyker Turf Field A Small Sided  - A</t>
         </is>
       </c>
       <c r="H9" s="0" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="I9" s="0" t="inlineStr">
         <is>
-          <t>Scheduled</t>
+          <t>Rescheduled</t>
         </is>
       </c>
     </row>

--- a/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
+++ b/data/2026/cjsl/fall/rebels-legacy-soccer-club-2014-2015.xlsx
@@ -74,7 +74,7 @@
     <col min="2" max="2" bestFit="1" customWidth="1" width="28.6"/>
     <col min="3" max="3" bestFit="1" customWidth="1" width="13.200000000000001"/>
     <col min="4" max="4" bestFit="1" customWidth="1" width="33.0"/>
-    <col min="5" max="5" bestFit="1" customWidth="1" width="7.700000000000001"/>
+    <col min="5" max="5" bestFit="1" customWidth="1" width="8.8"/>
     <col min="6" max="6" bestFit="1" customWidth="1" width="33.0"/>
     <col min="7" max="7" bestFit="1" customWidth="1" width="49.50000000000001"/>
     <col min="8" max="8" bestFit="1" customWidth="1" width="18.700000000000003"/>
@@ -284,7 +284,7 @@
       </c>
       <c r="E5" s="0" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0 - 10</t>
         </is>
       </c>
       <c r="F5" s="0" t="inlineStr">
@@ -304,7 +304,7 @@
       </c>
       <c r="I5" s="0" t="inlineStr">
         <is>
-          <t/>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
